--- a/audit/deftbrain-categories.xlsx
+++ b/audit/deftbrain-categories.xlsx
@@ -13,14 +13,14 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Category — Tool (flat)'!$A$1:$D$227</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,65 +36,13 @@
       <sz val="11"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Helvetica"/>
       <family val="2"/>
-      <i val="1"/>
-      <color rgb="FF6E6659"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color rgb="FF1E2A3A"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color rgb="FF1155CC"/>
-      <sz val="10"/>
-      <u val="single"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <i val="1"/>
-      <color rgb="FF6E6659"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color rgb="FF1E2A3A"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <i val="1"/>
-      <color rgb="FF6E6659"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
+      <color rgb="FF0B0B0B"/>
+      <sz val="14"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -106,13 +54,8 @@
         <fgColor rgb="FF1E2A3A"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9EDD8"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -121,64 +64,26 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFE8E1D5"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFE8E1D5"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFE8E1D5"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFE8E1D5"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFE8E1D5"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFE8E1D5"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -544,10 +449,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="16"/>
+    <col width="24" customWidth="1" min="1" max="10"/>
+    <col width="24" customWidth="1" min="12" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -588,51 +494,41 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>💪 Body</t>
+          <t>🗣️ Discourse</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>🗣️ Discourse</t>
+          <t>🔬 Go Deep!</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>🔬 Go Deep!</t>
+          <t>🧩 Diversions</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>🧩 Diversions</t>
+          <t>🪞 Me</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>🪞 Me</t>
+          <t>✨ What If?</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>✨ What If?</t>
+          <t>🧭 Veer</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>🧭 Veer</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
           <t>✅ Do It!</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>🎲 Detour</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="26" customHeight="1">
+    </row>
+    <row r="2" ht="26" customHeight="1" thickBot="1">
       <c r="A2" t="inlineStr">
         <is>
           <t>home · household · daily life</t>
@@ -665,51 +561,36 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>focus · stamina · regulation</t>
+          <t>mind · body · fuel</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>health · exercise · medical</t>
+          <t>say it well</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>say it well</t>
+          <t>research · learning · knowledge</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>research · learning · knowledge</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>curiosity · hobbies · intellect</t>
+          <t>fun · curiosity · play</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>self · reflection · growth</t>
+          <t>imagination · creativity</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>imagination · creativity</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
           <t>decisions · direction · choices</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>fun · play · diversions</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
+    </row>
+    <row r="3" ht="16" customHeight="1" thickTop="1">
       <c r="A3" t="inlineStr">
         <is>
           <t>Bike Medic</t>
@@ -747,7 +628,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Doctor Visit Prep</t>
+          <t>Analogy Engine</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -757,37 +638,27 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Analogy Engine</t>
+          <t>Argue Better</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Argue Better</t>
+          <t>Belief Stress Test</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Belief Stress Test</t>
+          <t>Alternate Path</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Alternate Path</t>
+          <t>Buy Wise</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Buy Wise</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
           <t>Batch Flow</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Alternate Path</t>
         </is>
       </c>
     </row>
@@ -829,12 +700,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Doctor Visit Translator</t>
+          <t>Apology Calibrator</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Apology Calibrator</t>
+          <t>Belief Stress Test</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -844,32 +715,22 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Belief Stress Test</t>
+          <t>Brain Dump Buddy</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
+          <t>Chaos Pilot</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Chaos Pilot</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>Brain Dump Buddy</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Chaos Pilot</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Chaos Pilot</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Brain Dump Buddy</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Bookmark</t>
         </is>
       </c>
     </row>
@@ -911,54 +772,44 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Lazy Workout Adapter</t>
+          <t>Argue Better</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Argue Better</t>
+          <t>HistoryToday</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>HistoryToday</t>
+          <t>Bookmark</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Bookmark</t>
+          <t>Brain State Deejay</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Brain State Deejay</t>
+          <t>Fan Theory</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Fan Theory</t>
+          <t>Crowd Wisdom</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Crowd Wisdom</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
           <t>Buy Wise</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Brain Roulette</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Drive Home</t>
+          <t>Doctor Visit Prep</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -993,54 +844,44 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Mental Health Navigator</t>
+          <t>Awkward Silence Filler</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Awkward Silence Filler</t>
+          <t>Jargon Assassin</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Jargon Assassin</t>
+          <t>Brain Roulette</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Brain Roulette</t>
+          <t>Crash Predictor</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Crash Predictor</t>
+          <t>Name Storm</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Name Storm</t>
+          <t>Decision Coach</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Decision Coach</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
           <t>Crisis Prioritizer</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Comeback Cooker</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Final Wish</t>
+          <t>Doctor Visit Translator</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1075,54 +916,44 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Procedure Probe</t>
+          <t>Caption Magic</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Caption Magic</t>
+          <t>Plain Talk — Document Analyst</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Plain Talk — Document Analyst</t>
+          <t>Comeback Cooker</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Crowd Wisdom</t>
+          <t>Dream Pattern Spotter</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Dream Pattern Spotter</t>
+          <t>Plot Twist</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Plot Twist</t>
+          <t>Future Proof</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Future Proof</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
           <t>Email Urgency Triager</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Fan Theory</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Jargon Assassin</t>
+          <t>Drive Home</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1157,54 +988,44 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sensory Minefield Mapper</t>
+          <t>Cold Open Craft</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Cold Open Craft</t>
+          <t>Pronounce It Right</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Pronounce It Right</t>
+          <t>Crowd Wisdom</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>HistoryToday</t>
+          <t>Final Wish</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Final Wish</t>
+          <t>Time Warp</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Time Warp</t>
+          <t>Idea Autopsy</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Idea Autopsy</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
           <t>Focus Pocus</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Hobby Match</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LaundroMat</t>
+          <t>Final Wish</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1239,66 +1060,56 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>SleepArchitect</t>
+          <t>Comeback Cooker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Comeback Cooker</t>
+          <t>Research Decoder</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Research Decoder</t>
+          <t>HistoryToday</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Markup Detective</t>
+          <t>Gentle Push Generator</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Gentle Push Generator</t>
+          <t>Which Life?</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Which Life?</t>
+          <t>Leverage Logic</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Leverage Logic</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
           <t>Task Avalanche Breaker</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Micro-Adventure Mapper</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Jargon Assassin</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Final Wish</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>Lease Trap Detector</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Final Wish</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Lease Trap Detector</t>
-        </is>
-      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>Leverage Logic</t>
@@ -1314,51 +1125,46 @@
           <t>GriefGuide</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Complaint Escalation Writer</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Complaint Escalation Writer</t>
+          <t>Signal vs. Noise</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Signal vs. Noise</t>
+          <t>Markup Detective</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Plot Hole</t>
+          <t>GriefGuide</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>GriefGuide</t>
+          <t>Wrong Answers Only</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Wrong Answers Only</t>
+          <t>Name Audit</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Name Audit</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
           <t>The Debrief</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Name That Feeling</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mise en Place</t>
+          <t>LaundroMat</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1386,46 +1192,41 @@
           <t>Lazy Workout Adapter</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Conflict Coach</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Conflict Coach</t>
+          <t>The Crux</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>The Crux</t>
+          <t>Plot Hole</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Roast Me</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
           <t>Luck Surface</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>One Percenter</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>One Percenter</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
           <t>Tool Finder</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Plot Hole</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Paperwork Path</t>
+          <t>Lease Trap Detector</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1448,46 +1249,41 @@
           <t>Mental Health Navigator</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Context Collapse</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Context Collapse</t>
+          <t>The Final Word</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>The Final Word</t>
+          <t>Roast Me</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Six Degrees of Me</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
           <t>Name That Feeling</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Plot Twist</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Plot Twist</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
           <t>Virtual Body Double</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Roast Me</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Pet Weirdness Decoder</t>
+          <t>Mise en Place</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1510,46 +1306,41 @@
           <t>Name That Feeling</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Difficult Talk Coach</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Difficult Talk Coach</t>
+          <t>The Gap</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>The Gap</t>
+          <t>Six Degrees of Me</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Time Warp</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
           <t>Nerve Check</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Pre-Mortem</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Pre-Mortem</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
           <t>Waiting Mode Liberator</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Time Warp</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Plant Rescue</t>
+          <t>Paperwork Path</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1572,41 +1363,36 @@
           <t>Nerve Check</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Ghost Writer</t>
         </is>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Time Warp</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Tip of Tongue</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
           <t>One Percenter</t>
         </is>
       </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Skill Gap Map</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Skill Gap Map</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
           <t>Where Did the Time Go?</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Tip of Tongue</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Recipe Chaos Solver</t>
+          <t>Pet Weirdness Decoder</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1629,43 +1415,43 @@
           <t>PEP-Personal Energy Planner</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Gratitude Debt Clearer</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Tip of Tongue</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>PEP-Personal Energy Planner</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>Which Life?</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Wrong Answers Only</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Plant Rescue</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Money Diplomat</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>Renter's Deposit Saver</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Money Diplomat</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Renter's Deposit Saver</t>
-        </is>
-      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>The Run-Through</t>
@@ -1673,15 +1459,15 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SleepArchitect</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
+          <t>Sensory Minefield Mapper</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
         <is>
           <t>Magic Mouth (M²)</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>Sensory Minefield Mapper</t>
         </is>
@@ -1690,7 +1476,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Roommate Court</t>
+          <t>Procedure Probe</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1705,15 +1491,15 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Social Battery Advisor</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
+          <t>SleepArchitect</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
         <is>
           <t>Pronounce It Right</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>Six Degrees of Me</t>
         </is>
@@ -1722,7 +1508,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Rulebook Breaker</t>
+          <t>Recipe Chaos Solver</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1737,15 +1523,15 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Spiral Stopper</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
+          <t>Social Battery Advisor</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
         <is>
           <t>The Alibi</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>Spiral Stopper</t>
         </is>
@@ -1754,7 +1540,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Safe Walk</t>
+          <t>Renter's Deposit Saver</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1769,15 +1555,15 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Task Avalanche Breaker</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
+          <t>Spiral Stopper</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
         <is>
           <t>The Final Word</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>Truth Bomb</t>
         </is>
@@ -1786,69 +1572,92 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Roommate Court</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Social Battery Advisor</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Ticket Tackler</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Task Avalanche Breaker</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Toast Writer</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>What's My Vibe</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Rulebook Breaker</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Toast Writer</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Upsell Shield</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Virtual Body Double</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Velvet Hammer</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Where Did the Time Go?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Safe Walk</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Velvet Hammer</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Waiting Mode Liberator</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>Wardrobe Chaos Helper</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Social Battery Advisor</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Ticket Tackler</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Virtual Body Double</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Toast Writer</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>What's My Vibe</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Toast Writer</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Upsell Shield</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Waiting Mode Liberator</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Velvet Hammer</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Where Did the Time Go?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Velvet Hammer</t>
-        </is>
-      </c>
-    </row>
+    </row>
+    <row r="26" ht="18" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -1861,7 +1670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D221"/>
+  <dimension ref="A1:D206"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1871,22 +1680,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Emoji</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Tool Name</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Tool URL</t>
         </is>
@@ -1971,12 +1780,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Drive Home</t>
+          <t>Doctor Visit Prep</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/DriveHome</t>
+          <t>https://deftbrain.com/DoctorVisitPrep</t>
         </is>
       </c>
     </row>
@@ -1993,12 +1802,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Final Wish</t>
+          <t>Doctor Visit Translator</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/FinalWish</t>
+          <t>https://deftbrain.com/DoctorVisitTranslator</t>
         </is>
       </c>
     </row>
@@ -2015,12 +1824,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jargon Assassin</t>
+          <t>Drive Home</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/JargonAssassin</t>
+          <t>https://deftbrain.com/DriveHome</t>
         </is>
       </c>
     </row>
@@ -2037,12 +1846,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LaundroMat</t>
+          <t>Final Wish</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/LaundroMat</t>
+          <t>https://deftbrain.com/FinalWish</t>
         </is>
       </c>
     </row>
@@ -2059,12 +1868,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lease Trap Detector</t>
+          <t>Jargon Assassin</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/LeaseTrapDetector</t>
+          <t>https://deftbrain.com/JargonAssassin</t>
         </is>
       </c>
     </row>
@@ -2081,12 +1890,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mise en Place</t>
+          <t>LaundroMat</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/MiseEnPlace</t>
+          <t>https://deftbrain.com/LaundroMat</t>
         </is>
       </c>
     </row>
@@ -2103,12 +1912,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Paperwork Path</t>
+          <t>Lease Trap Detector</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/PaperworkPath</t>
+          <t>https://deftbrain.com/LeaseTrapDetector</t>
         </is>
       </c>
     </row>
@@ -2125,12 +1934,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pet Weirdness Decoder</t>
+          <t>Mise en Place</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/PetWeirdnessDecoder</t>
+          <t>https://deftbrain.com/MiseEnPlace</t>
         </is>
       </c>
     </row>
@@ -2147,12 +1956,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Plant Rescue</t>
+          <t>Paperwork Path</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/PlantRescue</t>
+          <t>https://deftbrain.com/PaperworkPath</t>
         </is>
       </c>
     </row>
@@ -2169,12 +1978,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Recipe Chaos Solver</t>
+          <t>Pet Weirdness Decoder</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/RecipeChaosSolver</t>
+          <t>https://deftbrain.com/PetWeirdnessDecoder</t>
         </is>
       </c>
     </row>
@@ -2191,12 +2000,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Renter's Deposit Saver</t>
+          <t>Plant Rescue</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/RentersDepositSaver</t>
+          <t>https://deftbrain.com/PlantRescue</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2022,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Roommate Court</t>
+          <t>Procedure Probe</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/RoommateCourt</t>
+          <t>https://deftbrain.com/ProcedureProbe</t>
         </is>
       </c>
     </row>
@@ -2235,12 +2044,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Rulebook Breaker</t>
+          <t>Recipe Chaos Solver</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/RulebookBreaker</t>
+          <t>https://deftbrain.com/RecipeChaosSolver</t>
         </is>
       </c>
     </row>
@@ -2257,12 +2066,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Safe Walk</t>
+          <t>Renter's Deposit Saver</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/SafeWalk</t>
+          <t>https://deftbrain.com/RentersDepositSaver</t>
         </is>
       </c>
     </row>
@@ -2279,78 +2088,78 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Wardrobe Chaos Helper</t>
+          <t>Roommate Court</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/WardrobeChaosHelper</t>
+          <t>https://deftbrain.com/RoommateCourt</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Out &amp; About</t>
+          <t>The Grind</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>🗺️</t>
+          <t>🌅</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Culture Briefing</t>
+          <t>Rulebook Breaker</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/CultureBriefing</t>
+          <t>https://deftbrain.com/RulebookBreaker</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Out &amp; About</t>
+          <t>The Grind</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>🗺️</t>
+          <t>🌅</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Date Night</t>
+          <t>Safe Walk</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/DateNight</t>
+          <t>https://deftbrain.com/SafeWalk</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Out &amp; About</t>
+          <t>The Grind</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>🗺️</t>
+          <t>🌅</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hobby Match</t>
+          <t>Wardrobe Chaos Helper</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/HobbyMatch</t>
+          <t>https://deftbrain.com/WardrobeChaosHelper</t>
         </is>
       </c>
     </row>
@@ -2367,12 +2176,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Layover Maximizer</t>
+          <t>Culture Briefing</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/LayoverMaximizer</t>
+          <t>https://deftbrain.com/CultureBriefing</t>
         </is>
       </c>
     </row>
@@ -2389,12 +2198,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Micro-Adventure Mapper</t>
+          <t>Date Night</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/MicroAdventureMapper</t>
+          <t>https://deftbrain.com/DateNight</t>
         </is>
       </c>
     </row>
@@ -2411,12 +2220,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Party Architect</t>
+          <t>Hobby Match</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/PartyArchitect</t>
+          <t>https://deftbrain.com/HobbyMatch</t>
         </is>
       </c>
     </row>
@@ -2433,78 +2242,78 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sensory Minefield Mapper</t>
+          <t>Layover Maximizer</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/SensoryMinefieldMapper</t>
+          <t>https://deftbrain.com/LayoverMaximizer</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Humans</t>
+          <t>Out &amp; About</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>👥</t>
+          <t>🗺️</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Apology Calibrator</t>
+          <t>Micro-Adventure Mapper</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/ApologyCalibrator</t>
+          <t>https://deftbrain.com/MicroAdventureMapper</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Humans</t>
+          <t>Out &amp; About</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>👥</t>
+          <t>🗺️</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Awkward Silence Filler</t>
+          <t>Party Architect</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/AwkwardSilenceFiller</t>
+          <t>https://deftbrain.com/PartyArchitect</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Humans</t>
+          <t>Out &amp; About</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>👥</t>
+          <t>🗺️</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Comeback Cooker</t>
+          <t>Sensory Minefield Mapper</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/ComebackCooker</t>
+          <t>https://deftbrain.com/SensoryMinefieldMapper</t>
         </is>
       </c>
     </row>
@@ -2521,12 +2330,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Conflict Coach</t>
+          <t>Apology Calibrator</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/ConflictCoach</t>
+          <t>https://deftbrain.com/ApologyCalibrator</t>
         </is>
       </c>
     </row>
@@ -2543,12 +2352,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Date Night</t>
+          <t>Awkward Silence Filler</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/DateNight</t>
+          <t>https://deftbrain.com/AwkwardSilenceFiller</t>
         </is>
       </c>
     </row>
@@ -2565,12 +2374,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Decoder Ring</t>
+          <t>Comeback Cooker</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/DecoderRing</t>
+          <t>https://deftbrain.com/ComebackCooker</t>
         </is>
       </c>
     </row>
@@ -2587,12 +2396,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Difficult Talk Coach</t>
+          <t>Conflict Coach</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/DifficultTalkCoach</t>
+          <t>https://deftbrain.com/ConflictCoach</t>
         </is>
       </c>
     </row>
@@ -2609,12 +2418,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Final Wish</t>
+          <t>Date Night</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/FinalWish</t>
+          <t>https://deftbrain.com/DateNight</t>
         </is>
       </c>
     </row>
@@ -2631,12 +2440,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Friendship Fade Alerter</t>
+          <t>Decoder Ring</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/FriendshipFadeAlerter</t>
+          <t>https://deftbrain.com/DecoderRing</t>
         </is>
       </c>
     </row>
@@ -2653,12 +2462,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Giftology</t>
+          <t>Difficult Talk Coach</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/Giftology</t>
+          <t>https://deftbrain.com/DifficultTalkCoach</t>
         </is>
       </c>
     </row>
@@ -2675,12 +2484,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Gratitude Debt Clearer</t>
+          <t>Final Wish</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/GratitudeDebtClearer</t>
+          <t>https://deftbrain.com/FinalWish</t>
         </is>
       </c>
     </row>
@@ -2697,12 +2506,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Gravity Well</t>
+          <t>Friendship Fade Alerter</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/GravityWell</t>
+          <t>https://deftbrain.com/FriendshipFadeAlerter</t>
         </is>
       </c>
     </row>
@@ -2719,12 +2528,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Luck Surface</t>
+          <t>Giftology</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/LuckSurface</t>
+          <t>https://deftbrain.com/Giftology</t>
         </is>
       </c>
     </row>
@@ -2741,12 +2550,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Money Diplomat</t>
+          <t>Gratitude Debt Clearer</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/MoneyDiplomat</t>
+          <t>https://deftbrain.com/GratitudeDebtClearer</t>
         </is>
       </c>
     </row>
@@ -2763,12 +2572,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Party Architect</t>
+          <t>Gravity Well</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/PartyArchitect</t>
+          <t>https://deftbrain.com/GravityWell</t>
         </is>
       </c>
     </row>
@@ -2785,12 +2594,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Read the Room</t>
+          <t>Luck Surface</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/ReadTheRoom</t>
+          <t>https://deftbrain.com/LuckSurface</t>
         </is>
       </c>
     </row>
@@ -2807,12 +2616,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Roommate Court</t>
+          <t>Money Diplomat</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/RoommateCourt</t>
+          <t>https://deftbrain.com/MoneyDiplomat</t>
         </is>
       </c>
     </row>
@@ -2829,12 +2638,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Social Battery Advisor</t>
+          <t>Party Architect</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/SocialBatteryAdvisor</t>
+          <t>https://deftbrain.com/PartyArchitect</t>
         </is>
       </c>
     </row>
@@ -2851,12 +2660,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Toast Writer</t>
+          <t>Read the Room</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/ToastWriter</t>
+          <t>https://deftbrain.com/ReadTheRoom</t>
         </is>
       </c>
     </row>
@@ -2873,78 +2682,78 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Velvet Hammer</t>
+          <t>Roommate Court</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/VelvetHammer</t>
+          <t>https://deftbrain.com/RoommateCourt</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Loot</t>
+          <t>Humans</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>💰</t>
+          <t>👥</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bill Rescue</t>
+          <t>Social Battery Advisor</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/BillRescue</t>
+          <t>https://deftbrain.com/SocialBatteryAdvisor</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Loot</t>
+          <t>Humans</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>💰</t>
+          <t>👥</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Buy Wise</t>
+          <t>Toast Writer</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/BuyWise</t>
+          <t>https://deftbrain.com/ToastWriter</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Loot</t>
+          <t>Humans</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>💰</t>
+          <t>👥</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Complaint Escalation Writer</t>
+          <t>Velvet Hammer</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/ComplaintEscalationWriter</t>
+          <t>https://deftbrain.com/VelvetHammer</t>
         </is>
       </c>
     </row>
@@ -2961,12 +2770,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Contract Decoder</t>
+          <t>Bill Rescue</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/ContractDecoder</t>
+          <t>https://deftbrain.com/BillRescue</t>
         </is>
       </c>
     </row>
@@ -2983,12 +2792,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cut to the Chase</t>
+          <t>Buy Wise</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/CutToTheChase</t>
+          <t>https://deftbrain.com/BuyWise</t>
         </is>
       </c>
     </row>
@@ -3005,12 +2814,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Fake Review Detective</t>
+          <t>Complaint Escalation Writer</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/FakeReviewDetective</t>
+          <t>https://deftbrain.com/ComplaintEscalationWriter</t>
         </is>
       </c>
     </row>
@@ -3027,12 +2836,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Giftology</t>
+          <t>Contract Decoder</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/Giftology</t>
+          <t>https://deftbrain.com/ContractDecoder</t>
         </is>
       </c>
     </row>
@@ -3049,12 +2858,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Lease Trap Detector</t>
+          <t>Cut to the Chase</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/LeaseTrapDetector</t>
+          <t>https://deftbrain.com/CutToTheChase</t>
         </is>
       </c>
     </row>
@@ -3071,12 +2880,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Magic Mouth (M²)</t>
+          <t>Fake Review Detective</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/MagicMouth</t>
+          <t>https://deftbrain.com/FakeReviewDetective</t>
         </is>
       </c>
     </row>
@@ -3093,12 +2902,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Markup Detective</t>
+          <t>Giftology</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/MarkupDetective</t>
+          <t>https://deftbrain.com/Giftology</t>
         </is>
       </c>
     </row>
@@ -3115,12 +2924,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Money Diplomat</t>
+          <t>Lease Trap Detector</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/MoneyDiplomat</t>
+          <t>https://deftbrain.com/LeaseTrapDetector</t>
         </is>
       </c>
     </row>
@@ -3137,12 +2946,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Procedure Probe</t>
+          <t>Magic Mouth (M²)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/ProcedureProbe</t>
+          <t>https://deftbrain.com/MagicMouth</t>
         </is>
       </c>
     </row>
@@ -3159,12 +2968,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Quote Check</t>
+          <t>Markup Detective</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/QuoteCheck</t>
+          <t>https://deftbrain.com/MarkupDetective</t>
         </is>
       </c>
     </row>
@@ -3181,12 +2990,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Renter's Deposit Saver</t>
+          <t>Money Diplomat</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/RentersDepositSaver</t>
+          <t>https://deftbrain.com/MoneyDiplomat</t>
         </is>
       </c>
     </row>
@@ -3203,12 +3012,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Rulebook Breaker</t>
+          <t>Procedure Probe</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/RulebookBreaker</t>
+          <t>https://deftbrain.com/ProcedureProbe</t>
         </is>
       </c>
     </row>
@@ -3225,12 +3034,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Scam Radar</t>
+          <t>Quote Check</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/ScamRadar</t>
+          <t>https://deftbrain.com/QuoteCheck</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3056,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Subscription Tamer</t>
+          <t>Renter's Deposit Saver</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/SubscriptionTamer</t>
+          <t>https://deftbrain.com/RentersDepositSaver</t>
         </is>
       </c>
     </row>
@@ -3269,12 +3078,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ticket Tackler</t>
+          <t>Rulebook Breaker</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/TicketTackler</t>
+          <t>https://deftbrain.com/RulebookBreaker</t>
         </is>
       </c>
     </row>
@@ -3291,78 +3100,78 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Upsell Shield</t>
+          <t>Scam Radar</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/UpsellShield</t>
+          <t>https://deftbrain.com/ScamRadar</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Pursuits</t>
+          <t>Loot</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>🚀</t>
+          <t>💰</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Brag Sheet Builder</t>
+          <t>Subscription Tamer</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/BragSheetBuilder</t>
+          <t>https://deftbrain.com/SubscriptionTamer</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Pursuits</t>
+          <t>Loot</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>🚀</t>
+          <t>💰</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Caption Magic</t>
+          <t>Ticket Tackler</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/CaptionMagic</t>
+          <t>https://deftbrain.com/TicketTackler</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Pursuits</t>
+          <t>Loot</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>🚀</t>
+          <t>💰</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cold Open Craft</t>
+          <t>Upsell Shield</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/ColdOpenCraft</t>
+          <t>https://deftbrain.com/UpsellShield</t>
         </is>
       </c>
     </row>
@@ -3379,12 +3188,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Future Proof</t>
+          <t>Brag Sheet Builder</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/FutureProof</t>
+          <t>https://deftbrain.com/BragSheetBuilder</t>
         </is>
       </c>
     </row>
@@ -3401,12 +3210,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ghost Writer</t>
+          <t>Caption Magic</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/GhostWriter</t>
+          <t>https://deftbrain.com/CaptionMagic</t>
         </is>
       </c>
     </row>
@@ -3423,12 +3232,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Gravity Well</t>
+          <t>Cold Open Craft</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/GravityWell</t>
+          <t>https://deftbrain.com/ColdOpenCraft</t>
         </is>
       </c>
     </row>
@@ -3445,12 +3254,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Idea Autopsy</t>
+          <t>Future Proof</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/IdeaAutopsy</t>
+          <t>https://deftbrain.com/FutureProof</t>
         </is>
       </c>
     </row>
@@ -3467,12 +3276,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Leverage Logic</t>
+          <t>Ghost Writer</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/LeverageLogic</t>
+          <t>https://deftbrain.com/GhostWriter</t>
         </is>
       </c>
     </row>
@@ -3489,12 +3298,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Luck Surface</t>
+          <t>Gravity Well</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/LuckSurface</t>
+          <t>https://deftbrain.com/GravityWell</t>
         </is>
       </c>
     </row>
@@ -3511,12 +3320,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Name Audit</t>
+          <t>Idea Autopsy</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/NameAudit</t>
+          <t>https://deftbrain.com/IdeaAutopsy</t>
         </is>
       </c>
     </row>
@@ -3533,12 +3342,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Name Storm</t>
+          <t>Leverage Logic</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/NameStorm</t>
+          <t>https://deftbrain.com/LeverageLogic</t>
         </is>
       </c>
     </row>
@@ -3555,12 +3364,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Skill Gap Map</t>
+          <t>Luck Surface</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/SkillGapMap</t>
+          <t>https://deftbrain.com/LuckSurface</t>
         </is>
       </c>
     </row>
@@ -3577,12 +3386,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>The Alibi</t>
+          <t>Name Audit</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/TheAlibi</t>
+          <t>https://deftbrain.com/NameAudit</t>
         </is>
       </c>
     </row>
@@ -3599,78 +3408,78 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>The Run-Through</t>
+          <t>Name Storm</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/TheRunthrough</t>
+          <t>https://deftbrain.com/NameStorm</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>The Office</t>
+          <t>Pursuits</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>🏢</t>
+          <t>🚀</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Batch Flow</t>
+          <t>Skill Gap Map</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/BatchFlow</t>
+          <t>https://deftbrain.com/SkillGapMap</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>The Office</t>
+          <t>Pursuits</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>🏢</t>
+          <t>🚀</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brag Sheet Builder</t>
+          <t>The Alibi</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/BragSheetBuilder</t>
+          <t>https://deftbrain.com/TheAlibi</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>The Office</t>
+          <t>Pursuits</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>🏢</t>
+          <t>🚀</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Email Urgency Triager</t>
+          <t>The Run-Through</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/EmailUrgencyTriager</t>
+          <t>https://deftbrain.com/TheRunthrough</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3496,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Heckler Prep</t>
+          <t>Batch Flow</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/HecklerPrep</t>
+          <t>https://deftbrain.com/BatchFlow</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3518,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Meeting BS Detector</t>
+          <t>Brag Sheet Builder</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/MeetingBSDetector</t>
+          <t>https://deftbrain.com/BragSheetBuilder</t>
         </is>
       </c>
     </row>
@@ -3731,12 +3540,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Meeting Hijack Preventer</t>
+          <t>Email Urgency Triager</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/MeetingHijackPreventer</t>
+          <t>https://deftbrain.com/EmailUrgencyTriager</t>
         </is>
       </c>
     </row>
@@ -3753,12 +3562,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Pre-Mortem</t>
+          <t>Heckler Prep</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/PreMortem</t>
+          <t>https://deftbrain.com/HecklerPrep</t>
         </is>
       </c>
     </row>
@@ -3775,12 +3584,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>The Debrief</t>
+          <t>Meeting BS Detector</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/TheDebrief</t>
+          <t>https://deftbrain.com/MeetingBSDetector</t>
         </is>
       </c>
     </row>
@@ -3797,78 +3606,78 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>The Run-Through</t>
+          <t>Meeting Hijack Preventer</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/TheRunthrough</t>
+          <t>https://deftbrain.com/MeetingHijackPreventer</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>The Office</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>⚡</t>
+          <t>🏢</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Brain State Deejay</t>
+          <t>Pre-Mortem</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/BrainStateDeejay</t>
+          <t>https://deftbrain.com/PreMortem</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>The Office</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>⚡</t>
+          <t>🏢</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Crash Predictor</t>
+          <t>The Debrief</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/CrashPredictor</t>
+          <t>https://deftbrain.com/TheDebrief</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>The Office</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>⚡</t>
+          <t>🏢</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Crisis Prioritizer</t>
+          <t>The Run-Through</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/CrisisPrioritizer</t>
+          <t>https://deftbrain.com/TheRunthrough</t>
         </is>
       </c>
     </row>
@@ -3885,12 +3694,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Dream Pattern Spotter</t>
+          <t>Brain State Deejay</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/DreamPatternSpotter</t>
+          <t>https://deftbrain.com/BrainStateDeejay</t>
         </is>
       </c>
     </row>
@@ -3907,12 +3716,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Focus Pocus</t>
+          <t>Crash Predictor</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/FocusPocus</t>
+          <t>https://deftbrain.com/CrashPredictor</t>
         </is>
       </c>
     </row>
@@ -3929,12 +3738,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Focus Sound Architect</t>
+          <t>Crisis Prioritizer</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/FocusSoundArchitect</t>
+          <t>https://deftbrain.com/CrisisPrioritizer</t>
         </is>
       </c>
     </row>
@@ -3951,12 +3760,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Gentle Push Generator</t>
+          <t>Dream Pattern Spotter</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/GentlePushGenerator</t>
+          <t>https://deftbrain.com/DreamPatternSpotter</t>
         </is>
       </c>
     </row>
@@ -3973,12 +3782,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>GriefGuide</t>
+          <t>Focus Pocus</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/GriefGuide</t>
+          <t>https://deftbrain.com/FocusPocus</t>
         </is>
       </c>
     </row>
@@ -3995,12 +3804,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Lazy Workout Adapter</t>
+          <t>Focus Sound Architect</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/LazyWorkoutAdapter</t>
+          <t>https://deftbrain.com/FocusSoundArchitect</t>
         </is>
       </c>
     </row>
@@ -4017,12 +3826,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Mental Health Navigator</t>
+          <t>Gentle Push Generator</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/MentalHealthNavigator</t>
+          <t>https://deftbrain.com/GentlePushGenerator</t>
         </is>
       </c>
     </row>
@@ -4039,12 +3848,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Name That Feeling</t>
+          <t>GriefGuide</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/NameThatFeeling</t>
+          <t>https://deftbrain.com/GriefGuide</t>
         </is>
       </c>
     </row>
@@ -4061,12 +3870,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Nerve Check</t>
+          <t>Lazy Workout Adapter</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/NerveCheck</t>
+          <t>https://deftbrain.com/LazyWorkoutAdapter</t>
         </is>
       </c>
     </row>
@@ -4083,12 +3892,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>PEP-Personal Energy Planner</t>
+          <t>Mental Health Navigator</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/PEP</t>
+          <t>https://deftbrain.com/MentalHealthNavigator</t>
         </is>
       </c>
     </row>
@@ -4105,12 +3914,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>SleepArchitect</t>
+          <t>Name That Feeling</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/SleepArchitect</t>
+          <t>https://deftbrain.com/NameThatFeeling</t>
         </is>
       </c>
     </row>
@@ -4127,12 +3936,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Social Battery Advisor</t>
+          <t>Nerve Check</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/SocialBatteryAdvisor</t>
+          <t>https://deftbrain.com/NerveCheck</t>
         </is>
       </c>
     </row>
@@ -4149,12 +3958,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spiral Stopper</t>
+          <t>PEP-Personal Energy Planner</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/SpiralStopper</t>
+          <t>https://deftbrain.com/PEP</t>
         </is>
       </c>
     </row>
@@ -4171,12 +3980,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Task Avalanche Breaker</t>
+          <t>Sensory Minefield Mapper</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/TaskAvalancheBreaker</t>
+          <t>https://deftbrain.com/SensoryMinefieldMapper</t>
         </is>
       </c>
     </row>
@@ -4193,12 +4002,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Virtual Body Double</t>
+          <t>SleepArchitect</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/VirtualBodyDouble</t>
+          <t>https://deftbrain.com/SleepArchitect</t>
         </is>
       </c>
     </row>
@@ -4215,166 +4024,166 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Waiting Mode Liberator</t>
+          <t>Social Battery Advisor</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/WaitingModeLiberator</t>
+          <t>https://deftbrain.com/SocialBatteryAdvisor</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Body</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>💪</t>
+          <t>⚡</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Doctor Visit Prep</t>
+          <t>Spiral Stopper</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/DoctorVisitPrep</t>
+          <t>https://deftbrain.com/SpiralStopper</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Body</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>💪</t>
+          <t>⚡</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Doctor Visit Translator</t>
+          <t>Task Avalanche Breaker</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/DoctorVisitTranslator</t>
+          <t>https://deftbrain.com/TaskAvalancheBreaker</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Body</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>💪</t>
+          <t>⚡</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Lazy Workout Adapter</t>
+          <t>Virtual Body Double</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/LazyWorkoutAdapter</t>
+          <t>https://deftbrain.com/VirtualBodyDouble</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Body</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>💪</t>
+          <t>⚡</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Mental Health Navigator</t>
+          <t>Waiting Mode Liberator</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/MentalHealthNavigator</t>
+          <t>https://deftbrain.com/WaitingModeLiberator</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Body</t>
+          <t>Discourse</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>💪</t>
+          <t>🗣️</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Procedure Probe</t>
+          <t>Analogy Engine</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/ProcedureProbe</t>
+          <t>https://deftbrain.com/AnalogyEngine</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Body</t>
+          <t>Discourse</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>💪</t>
+          <t>🗣️</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Sensory Minefield Mapper</t>
+          <t>Apology Calibrator</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/SensoryMinefieldMapper</t>
+          <t>https://deftbrain.com/ApologyCalibrator</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Body</t>
+          <t>Discourse</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>💪</t>
+          <t>🗣️</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>SleepArchitect</t>
+          <t>Argue Better</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/SleepArchitect</t>
+          <t>https://deftbrain.com/ArgueBetter</t>
         </is>
       </c>
     </row>
@@ -4391,12 +4200,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Analogy Engine</t>
+          <t>Awkward Silence Filler</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/AnalogyEngine</t>
+          <t>https://deftbrain.com/AwkwardSilenceFiller</t>
         </is>
       </c>
     </row>
@@ -4413,12 +4222,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Apology Calibrator</t>
+          <t>Caption Magic</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/ApologyCalibrator</t>
+          <t>https://deftbrain.com/CaptionMagic</t>
         </is>
       </c>
     </row>
@@ -4435,12 +4244,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Argue Better</t>
+          <t>Cold Open Craft</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/ArgueBetter</t>
+          <t>https://deftbrain.com/ColdOpenCraft</t>
         </is>
       </c>
     </row>
@@ -4457,12 +4266,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Awkward Silence Filler</t>
+          <t>Comeback Cooker</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/AwkwardSilenceFiller</t>
+          <t>https://deftbrain.com/ComebackCooker</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4288,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Caption Magic</t>
+          <t>Complaint Escalation Writer</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/CaptionMagic</t>
+          <t>https://deftbrain.com/ComplaintEscalationWriter</t>
         </is>
       </c>
     </row>
@@ -4501,12 +4310,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Cold Open Craft</t>
+          <t>Conflict Coach</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/ColdOpenCraft</t>
+          <t>https://deftbrain.com/ConflictCoach</t>
         </is>
       </c>
     </row>
@@ -4523,12 +4332,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Comeback Cooker</t>
+          <t>Context Collapse</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/ComebackCooker</t>
+          <t>https://deftbrain.com/ContextCollapse</t>
         </is>
       </c>
     </row>
@@ -4545,12 +4354,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Complaint Escalation Writer</t>
+          <t>Difficult Talk Coach</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/ComplaintEscalationWriter</t>
+          <t>https://deftbrain.com/DifficultTalkCoach</t>
         </is>
       </c>
     </row>
@@ -4567,12 +4376,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Conflict Coach</t>
+          <t>Ghost Writer</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/ConflictCoach</t>
+          <t>https://deftbrain.com/GhostWriter</t>
         </is>
       </c>
     </row>
@@ -4589,12 +4398,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Context Collapse</t>
+          <t>Gratitude Debt Clearer</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/ContextCollapse</t>
+          <t>https://deftbrain.com/GratitudeDebtClearer</t>
         </is>
       </c>
     </row>
@@ -4611,12 +4420,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Difficult Talk Coach</t>
+          <t>Magic Mouth (M²)</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/DifficultTalkCoach</t>
+          <t>https://deftbrain.com/MagicMouth</t>
         </is>
       </c>
     </row>
@@ -4633,12 +4442,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Ghost Writer</t>
+          <t>Pronounce It Right</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/GhostWriter</t>
+          <t>https://deftbrain.com/PronounceItRight</t>
         </is>
       </c>
     </row>
@@ -4655,12 +4464,12 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Gratitude Debt Clearer</t>
+          <t>The Alibi</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/GratitudeDebtClearer</t>
+          <t>https://deftbrain.com/TheAlibi</t>
         </is>
       </c>
     </row>
@@ -4677,12 +4486,12 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Magic Mouth (M²)</t>
+          <t>The Final Word</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/MagicMouth</t>
+          <t>https://deftbrain.com/TheFinalWord</t>
         </is>
       </c>
     </row>
@@ -4699,12 +4508,12 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Pronounce It Right</t>
+          <t>Toast Writer</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/PronounceItRight</t>
+          <t>https://deftbrain.com/ToastWriter</t>
         </is>
       </c>
     </row>
@@ -4721,78 +4530,78 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>The Alibi</t>
+          <t>Velvet Hammer</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/TheAlibi</t>
+          <t>https://deftbrain.com/VelvetHammer</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Discourse</t>
+          <t>Go Deep!</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>🗣️</t>
+          <t>🔬</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>The Final Word</t>
+          <t>Analogy Engine</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/TheFinalWord</t>
+          <t>https://deftbrain.com/AnalogyEngine</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Discourse</t>
+          <t>Go Deep!</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>🗣️</t>
+          <t>🔬</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Toast Writer</t>
+          <t>Belief Stress Test</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/ToastWriter</t>
+          <t>https://deftbrain.com/BeliefStressTest</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Discourse</t>
+          <t>Go Deep!</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>🗣️</t>
+          <t>🔬</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Velvet Hammer</t>
+          <t>HistoryToday</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/VelvetHammer</t>
+          <t>https://deftbrain.com/HistoryToday</t>
         </is>
       </c>
     </row>
@@ -4809,12 +4618,12 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Analogy Engine</t>
+          <t>Jargon Assassin</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/AnalogyEngine</t>
+          <t>https://deftbrain.com/JargonAssassin</t>
         </is>
       </c>
     </row>
@@ -4831,12 +4640,12 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Belief Stress Test</t>
+          <t>Plain Talk — Document Analyst</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/BeliefStressTest</t>
+          <t>https://deftbrain.com/PlainTalk</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4662,12 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>HistoryToday</t>
+          <t>Pronounce It Right</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/HistoryToday</t>
+          <t>https://deftbrain.com/PronounceItRight</t>
         </is>
       </c>
     </row>
@@ -4875,12 +4684,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Jargon Assassin</t>
+          <t>Research Decoder</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/JargonAssassin</t>
+          <t>https://deftbrain.com/ResearchDecoder</t>
         </is>
       </c>
     </row>
@@ -4897,12 +4706,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Plain Talk — Document Analyst</t>
+          <t>Signal vs. Noise</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/PlainTalk</t>
+          <t>https://deftbrain.com/SignalVsNoise</t>
         </is>
       </c>
     </row>
@@ -4919,12 +4728,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Pronounce It Right</t>
+          <t>The Crux</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/PronounceItRight</t>
+          <t>https://deftbrain.com/TheCrux</t>
         </is>
       </c>
     </row>
@@ -4941,12 +4750,12 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Research Decoder</t>
+          <t>The Final Word</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/ResearchDecoder</t>
+          <t>https://deftbrain.com/TheFinalWord</t>
         </is>
       </c>
     </row>
@@ -4963,78 +4772,78 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Signal vs. Noise</t>
+          <t>The Gap</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/SignalVsNoise</t>
+          <t>https://deftbrain.com/TheGap</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Go Deep!</t>
+          <t>Diversions</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>🔬</t>
+          <t>🧩</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>The Crux</t>
+          <t>Argue Better</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/TheCrux</t>
+          <t>https://deftbrain.com/ArgueBetter</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Go Deep!</t>
+          <t>Diversions</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>🔬</t>
+          <t>🧩</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>The Final Word</t>
+          <t>Belief Stress Test</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/TheFinalWord</t>
+          <t>https://deftbrain.com/BeliefStressTest</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Go Deep!</t>
+          <t>Diversions</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>🔬</t>
+          <t>🧩</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>The Gap</t>
+          <t>Bookmark</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/TheGap</t>
+          <t>https://deftbrain.com/Bookmark</t>
         </is>
       </c>
     </row>
@@ -5051,12 +4860,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Argue Better</t>
+          <t>Brain Roulette</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/ArgueBetter</t>
+          <t>https://deftbrain.com/BrainRoulette</t>
         </is>
       </c>
     </row>
@@ -5073,12 +4882,12 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Belief Stress Test</t>
+          <t>Comeback Cooker</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/BeliefStressTest</t>
+          <t>https://deftbrain.com/ComebackCooker</t>
         </is>
       </c>
     </row>
@@ -5095,12 +4904,12 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Bookmark</t>
+          <t>Crowd Wisdom</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/Bookmark</t>
+          <t>https://deftbrain.com/CrowdWisdom</t>
         </is>
       </c>
     </row>
@@ -5117,12 +4926,12 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Brain Roulette</t>
+          <t>HistoryToday</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/BrainRoulette</t>
+          <t>https://deftbrain.com/HistoryToday</t>
         </is>
       </c>
     </row>
@@ -5139,12 +4948,12 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Crowd Wisdom</t>
+          <t>Markup Detective</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/CrowdWisdom</t>
+          <t>https://deftbrain.com/MarkupDetective</t>
         </is>
       </c>
     </row>
@@ -5161,12 +4970,12 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>HistoryToday</t>
+          <t>Plot Hole</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/HistoryToday</t>
+          <t>https://deftbrain.com/PlotHole</t>
         </is>
       </c>
     </row>
@@ -5183,12 +4992,12 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Markup Detective</t>
+          <t>Roast Me</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/MarkupDetective</t>
+          <t>https://deftbrain.com/RoastMe</t>
         </is>
       </c>
     </row>
@@ -5205,12 +5014,12 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Plot Hole</t>
+          <t>Six Degrees of Me</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/PlotHole</t>
+          <t>https://deftbrain.com/SixDegreesOfMe</t>
         </is>
       </c>
     </row>
@@ -5227,12 +5036,12 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Roast Me</t>
+          <t>Time Warp</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/RoastMe</t>
+          <t>https://deftbrain.com/TimeWarp</t>
         </is>
       </c>
     </row>
@@ -5249,56 +5058,56 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Six Degrees of Me</t>
+          <t>Tip of Tongue</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/SixDegreesOfMe</t>
+          <t>https://deftbrain.com/TipOfTongue</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Diversions</t>
+          <t>Me</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>🧩</t>
+          <t>🪞</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Time Warp</t>
+          <t>Belief Stress Test</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/TimeWarp</t>
+          <t>https://deftbrain.com/BeliefStressTest</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Diversions</t>
+          <t>Me</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>🧩</t>
+          <t>🪞</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Tip of Tongue</t>
+          <t>Brain Dump Buddy</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/TipOfTongue</t>
+          <t>https://deftbrain.com/BrainDumpBuddy</t>
         </is>
       </c>
     </row>
@@ -5315,12 +5124,12 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Belief Stress Test</t>
+          <t>Brain State Deejay</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/BeliefStressTest</t>
+          <t>https://deftbrain.com/BrainStateDeejay</t>
         </is>
       </c>
     </row>
@@ -5337,12 +5146,12 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Brain Dump Buddy</t>
+          <t>Crash Predictor</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/BrainDumpBuddy</t>
+          <t>https://deftbrain.com/CrashPredictor</t>
         </is>
       </c>
     </row>
@@ -5359,12 +5168,12 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Brain State Deejay</t>
+          <t>Dream Pattern Spotter</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/BrainStateDeejay</t>
+          <t>https://deftbrain.com/DreamPatternSpotter</t>
         </is>
       </c>
     </row>
@@ -5381,12 +5190,12 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Crash Predictor</t>
+          <t>Final Wish</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/CrashPredictor</t>
+          <t>https://deftbrain.com/FinalWish</t>
         </is>
       </c>
     </row>
@@ -5403,12 +5212,12 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Dream Pattern Spotter</t>
+          <t>Gentle Push Generator</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/DreamPatternSpotter</t>
+          <t>https://deftbrain.com/GentlePushGenerator</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5234,12 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Final Wish</t>
+          <t>GriefGuide</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/FinalWish</t>
+          <t>https://deftbrain.com/GriefGuide</t>
         </is>
       </c>
     </row>
@@ -5447,12 +5256,12 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Gentle Push Generator</t>
+          <t>Luck Surface</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/GentlePushGenerator</t>
+          <t>https://deftbrain.com/LuckSurface</t>
         </is>
       </c>
     </row>
@@ -5469,12 +5278,12 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>GriefGuide</t>
+          <t>Name That Feeling</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/GriefGuide</t>
+          <t>https://deftbrain.com/NameThatFeeling</t>
         </is>
       </c>
     </row>
@@ -5491,12 +5300,12 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Luck Surface</t>
+          <t>Nerve Check</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/LuckSurface</t>
+          <t>https://deftbrain.com/NerveCheck</t>
         </is>
       </c>
     </row>
@@ -5513,12 +5322,12 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Name That Feeling</t>
+          <t>One Percenter</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/NameThatFeeling</t>
+          <t>https://deftbrain.com/OnePercenter</t>
         </is>
       </c>
     </row>
@@ -5535,12 +5344,12 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Nerve Check</t>
+          <t>PEP-Personal Energy Planner</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/NerveCheck</t>
+          <t>https://deftbrain.com/PEP</t>
         </is>
       </c>
     </row>
@@ -5557,12 +5366,12 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>One Percenter</t>
+          <t>Sensory Minefield Mapper</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/OnePercenter</t>
+          <t>https://deftbrain.com/SensoryMinefieldMapper</t>
         </is>
       </c>
     </row>
@@ -5579,12 +5388,12 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>PEP-Personal Energy Planner</t>
+          <t>Six Degrees of Me</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/PEP</t>
+          <t>https://deftbrain.com/SixDegreesOfMe</t>
         </is>
       </c>
     </row>
@@ -5601,12 +5410,12 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Sensory Minefield Mapper</t>
+          <t>Spiral Stopper</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/SensoryMinefieldMapper</t>
+          <t>https://deftbrain.com/SpiralStopper</t>
         </is>
       </c>
     </row>
@@ -5623,12 +5432,12 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Six Degrees of Me</t>
+          <t>Truth Bomb</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/SixDegreesOfMe</t>
+          <t>https://deftbrain.com/TruthBomb</t>
         </is>
       </c>
     </row>
@@ -5645,12 +5454,12 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Spiral Stopper</t>
+          <t>What's My Vibe</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/SpiralStopper</t>
+          <t>https://deftbrain.com/WhatsMyVibe</t>
         </is>
       </c>
     </row>
@@ -5667,56 +5476,56 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Truth Bomb</t>
+          <t>Where Did the Time Go?</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/TruthBomb</t>
+          <t>https://deftbrain.com/WhereDidTheTimeGo</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Me</t>
+          <t>What If?</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>🪞</t>
+          <t>✨</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>What's My Vibe</t>
+          <t>Alternate Path</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/WhatsMyVibe</t>
+          <t>https://deftbrain.com/AlternatePath</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Me</t>
+          <t>What If?</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>🪞</t>
+          <t>✨</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Where Did the Time Go?</t>
+          <t>Chaos Pilot</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/WhereDidTheTimeGo</t>
+          <t>https://deftbrain.com/ChaosPilot</t>
         </is>
       </c>
     </row>
@@ -5733,12 +5542,12 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Alternate Path</t>
+          <t>Fan Theory</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/AlternatePath</t>
+          <t>https://deftbrain.com/FanTheory</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5564,12 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Chaos Pilot</t>
+          <t>Name Storm</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/ChaosPilot</t>
+          <t>https://deftbrain.com/NameStorm</t>
         </is>
       </c>
     </row>
@@ -5777,12 +5586,12 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Fan Theory</t>
+          <t>Plot Twist</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/FanTheory</t>
+          <t>https://deftbrain.com/PlotTwist</t>
         </is>
       </c>
     </row>
@@ -5799,12 +5608,12 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Name Storm</t>
+          <t>Time Warp</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/NameStorm</t>
+          <t>https://deftbrain.com/TimeWarp</t>
         </is>
       </c>
     </row>
@@ -5821,12 +5630,12 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Plot Twist</t>
+          <t>Which Life?</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/PlotTwist</t>
+          <t>https://deftbrain.com/WhichLife</t>
         </is>
       </c>
     </row>
@@ -5843,56 +5652,56 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Time Warp</t>
+          <t>Wrong Answers Only</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/TimeWarp</t>
+          <t>https://deftbrain.com/WrongAnswersOnly</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>What If?</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>✨</t>
+          <t>🧭</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Which Life?</t>
+          <t>Buy Wise</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/WhichLife</t>
+          <t>https://deftbrain.com/BuyWise</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>What If?</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>✨</t>
+          <t>🧭</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Wrong Answers Only</t>
+          <t>Chaos Pilot</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/WrongAnswersOnly</t>
+          <t>https://deftbrain.com/ChaosPilot</t>
         </is>
       </c>
     </row>
@@ -5909,12 +5718,12 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Buy Wise</t>
+          <t>Crowd Wisdom</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/BuyWise</t>
+          <t>https://deftbrain.com/CrowdWisdom</t>
         </is>
       </c>
     </row>
@@ -5931,12 +5740,12 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Chaos Pilot</t>
+          <t>Decision Coach</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/ChaosPilot</t>
+          <t>https://deftbrain.com/DecisionCoach</t>
         </is>
       </c>
     </row>
@@ -5953,12 +5762,12 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Crowd Wisdom</t>
+          <t>Future Proof</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/CrowdWisdom</t>
+          <t>https://deftbrain.com/FutureProof</t>
         </is>
       </c>
     </row>
@@ -5975,12 +5784,12 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Decision Coach</t>
+          <t>Idea Autopsy</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/DecisionCoach</t>
+          <t>https://deftbrain.com/IdeaAutopsy</t>
         </is>
       </c>
     </row>
@@ -5997,12 +5806,12 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Future Proof</t>
+          <t>Leverage Logic</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/FutureProof</t>
+          <t>https://deftbrain.com/LeverageLogic</t>
         </is>
       </c>
     </row>
@@ -6019,12 +5828,12 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Idea Autopsy</t>
+          <t>Name Audit</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/IdeaAutopsy</t>
+          <t>https://deftbrain.com/NameAudit</t>
         </is>
       </c>
     </row>
@@ -6041,12 +5850,12 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Leverage Logic</t>
+          <t>One Percenter</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/LeverageLogic</t>
+          <t>https://deftbrain.com/OnePercenter</t>
         </is>
       </c>
     </row>
@@ -6063,12 +5872,12 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Name Audit</t>
+          <t>Plot Twist</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/NameAudit</t>
+          <t>https://deftbrain.com/PlotTwist</t>
         </is>
       </c>
     </row>
@@ -6085,12 +5894,12 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>One Percenter</t>
+          <t>Pre-Mortem</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/OnePercenter</t>
+          <t>https://deftbrain.com/PreMortem</t>
         </is>
       </c>
     </row>
@@ -6107,12 +5916,12 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Plot Twist</t>
+          <t>Skill Gap Map</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/PlotTwist</t>
+          <t>https://deftbrain.com/SkillGapMap</t>
         </is>
       </c>
     </row>
@@ -6129,56 +5938,56 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Pre-Mortem</t>
+          <t>Which Life?</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/PreMortem</t>
+          <t>https://deftbrain.com/WhichLife</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Veer</t>
+          <t>Do It!</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>🧭</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Skill Gap Map</t>
+          <t>Batch Flow</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/SkillGapMap</t>
+          <t>https://deftbrain.com/BatchFlow</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Veer</t>
+          <t>Do It!</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>🧭</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Which Life?</t>
+          <t>Brain Dump Buddy</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/WhichLife</t>
+          <t>https://deftbrain.com/BrainDumpBuddy</t>
         </is>
       </c>
     </row>
@@ -6195,12 +6004,12 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Batch Flow</t>
+          <t>Buy Wise</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/BatchFlow</t>
+          <t>https://deftbrain.com/BuyWise</t>
         </is>
       </c>
     </row>
@@ -6217,12 +6026,12 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Brain Dump Buddy</t>
+          <t>Crisis Prioritizer</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/BrainDumpBuddy</t>
+          <t>https://deftbrain.com/CrisisPrioritizer</t>
         </is>
       </c>
     </row>
@@ -6239,12 +6048,12 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Buy Wise</t>
+          <t>Email Urgency Triager</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/BuyWise</t>
+          <t>https://deftbrain.com/EmailUrgencyTriager</t>
         </is>
       </c>
     </row>
@@ -6261,12 +6070,12 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Crisis Prioritizer</t>
+          <t>Focus Pocus</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/CrisisPrioritizer</t>
+          <t>https://deftbrain.com/FocusPocus</t>
         </is>
       </c>
     </row>
@@ -6283,12 +6092,12 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Email Urgency Triager</t>
+          <t>Task Avalanche Breaker</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/EmailUrgencyTriager</t>
+          <t>https://deftbrain.com/TaskAvalancheBreaker</t>
         </is>
       </c>
     </row>
@@ -6305,12 +6114,12 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Focus Pocus</t>
+          <t>The Debrief</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/FocusPocus</t>
+          <t>https://deftbrain.com/TheDebrief</t>
         </is>
       </c>
     </row>
@@ -6327,12 +6136,12 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Task Avalanche Breaker</t>
+          <t>Tool Finder</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/TaskAvalancheBreaker</t>
+          <t>https://deftbrain.com/ToolFinder</t>
         </is>
       </c>
     </row>
@@ -6349,12 +6158,12 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>The Debrief</t>
+          <t>Virtual Body Double</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/TheDebrief</t>
+          <t>https://deftbrain.com/VirtualBodyDouble</t>
         </is>
       </c>
     </row>
@@ -6371,12 +6180,12 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Tool Finder</t>
+          <t>Waiting Mode Liberator</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/ToolFinder</t>
+          <t>https://deftbrain.com/WaitingModeLiberator</t>
         </is>
       </c>
     </row>
@@ -6393,342 +6202,12 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Virtual Body Double</t>
+          <t>Where Did the Time Go?</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>https://deftbrain.com/VirtualBodyDouble</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>Do It!</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>Waiting Mode Liberator</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>https://deftbrain.com/WaitingModeLiberator</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>Do It!</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>Where Did the Time Go?</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
           <t>https://deftbrain.com/WhereDidTheTimeGo</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>Detour</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>🎲</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>Alternate Path</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>https://deftbrain.com/AlternatePath</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>Detour</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>🎲</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>Bookmark</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>https://deftbrain.com/Bookmark</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>Detour</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>🎲</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>Brain Roulette</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>https://deftbrain.com/BrainRoulette</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>Detour</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>🎲</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>Comeback Cooker</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>https://deftbrain.com/ComebackCooker</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>Detour</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>🎲</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>Fan Theory</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>https://deftbrain.com/FanTheory</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>Detour</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>🎲</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>Hobby Match</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>https://deftbrain.com/HobbyMatch</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>Detour</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>🎲</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>Micro-Adventure Mapper</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>https://deftbrain.com/MicroAdventureMapper</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>Detour</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>🎲</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>Name That Feeling</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>https://deftbrain.com/NameThatFeeling</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>Detour</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>🎲</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>Plot Hole</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>https://deftbrain.com/PlotHole</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>Detour</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>🎲</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>Roast Me</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>https://deftbrain.com/RoastMe</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>Detour</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>🎲</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>Time Warp</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>https://deftbrain.com/TimeWarp</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>Detour</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>🎲</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>Tip of Tongue</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>https://deftbrain.com/TipOfTongue</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>Detour</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>🎲</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>Wrong Answers Only</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>https://deftbrain.com/WrongAnswersOnly</t>
         </is>
       </c>
     </row>
@@ -6744,7 +6223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6754,22 +6233,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Emoji</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Subtitle</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Tool Count</t>
         </is>
@@ -6792,7 +6271,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -6908,201 +6387,161 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>focus · stamina · regulation</t>
+          <t>mind · body · fuel</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Body</t>
+          <t>Discourse</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>💪</t>
+          <t>🗣️</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>health · exercise · medical</t>
+          <t>say it well</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Discourse</t>
+          <t>Go Deep!</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🗣️</t>
+          <t>🔬</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>say it well</t>
+          <t>research · learning · knowledge</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Go Deep!</t>
+          <t>Diversions</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🔬</t>
+          <t>🧩</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>research · learning · knowledge</t>
+          <t>fun · curiosity · play</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Diversions</t>
+          <t>Me</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🧩</t>
+          <t>🪞</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>curiosity · play · intellect</t>
+          <t>self · reflection · growth</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Me</t>
+          <t>What If?</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🪞</t>
+          <t>✨</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>self · reflection · growth</t>
+          <t>imagination · creativity</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>What If?</t>
+          <t>Veer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>✨</t>
+          <t>🧭</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>imagination · creativity</t>
+          <t>decisions · direction · choices</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Veer</t>
+          <t>Do It!</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🧭</t>
+          <t>✅</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>decisions · direction · choices</t>
+          <t>execution · unstuck · tasks</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Do It!</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>execution · unstuck · tasks</t>
+          <t>Total placements</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Detour</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>🎲</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>fun · play · diversions</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Total placements</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>220</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>
